--- a/04_DESIGN_TABLES/DesignTable_2501LL.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2501LL.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O25"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -535,6 +535,11 @@
           <t>$PRP@OMiSKU</t>
         </is>
       </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>$PRP@DimSource</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
@@ -1470,24 +1475,50 @@
           <t>2501-LL-04-02-FG</t>
         </is>
       </c>
+      <c r="B19" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="E19" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.188</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.405</v>
+      </c>
       <c r="I19" t="inlineStr">
         <is>
           <t>2501-LL-04-02-FG</t>
         </is>
       </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>7/16-20 (JIC) x 1/8-27 (NPTF) N4 long pattern</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-LL-04-02 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-LL-04-02 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): M@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-04-02-FG col "M LGTH" = "0.890" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 538.9, page verified True) [Brennan = yes 2026-10-18] - JIC leg: crossing to the JIC tip (column mapping: REPORT.md, table 2501LL); N4@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-04-02-FG col "L LGTH" = "1.560" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 538.9, page verified True) [Brennan = yes 2026-10-18] - pipe leg: crossing to the male NPTF tip (column mapping: REPORT.md, table 2501LL); Y@REF: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-04-02-FG col "Y FLATS" = "0.438" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 538.9, page verified True) [Brennan = yes 2026-10-18] - forged body flats (column mapping: REPORT.md, table 2501LL); D@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-04-02-FG col "B1 DRILL" = "0.172" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 538.9, page verified True) [Brennan = yes 2026-10-18] - JIC-leg bore (column mapping: REPORT.md, table 2501LL); D1@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-04-02-FG col "A2 DRILL" = "0.188" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 538.9, page verified True) [Brennan = yes 2026-10-18] - pipe drill (column mapping: REPORT.md, table 2501LL); THDMAJ_B@DRIVE: end library: male JIC -04 thread major = 0.4375 (gen_straight2 JIC[4] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A@DRIVE: end library: pipe OD of the -02 NPTF thread = 0.405 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[2], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes in the format of the table's other rows; = Brennan TFA-p024-t02 thread columns (B1 SAE 37Deg 7/16-20, A2 NPTF 1/8-27) and OMi Items Side 1 / 2 / 3 Thread</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-04-02 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-04-02 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (wave2 tee_elbow, staged, not shipped): sizes from the Brennan TFA catalog, end details from the end library; marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate)</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
@@ -1498,6 +1529,11 @@
       <c r="O19" t="inlineStr">
         <is>
           <t>2501-LL-04-02-FG</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1507,24 +1543,50 @@
           <t>2501-LL-04-04-FG</t>
         </is>
       </c>
+      <c r="B20" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="E20" t="n">
+        <v>0.172</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.4375</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.54</v>
+      </c>
       <c r="I20" t="inlineStr">
         <is>
           <t>2501-LL-04-04-FG</t>
         </is>
       </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>7/16-20 (JIC) x 1/4-18 (NPTF) N4 long pattern</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-LL-04-04 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-LL-04-04 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): M@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-04-04-FG col "M LGTH" = "1.050" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 549.0, page verified True) [Brennan = yes 2026-10-18] - JIC leg: crossing to the JIC tip (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); N4@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-04-04-FG col "L LGTH" = "2.070" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 549.0, page verified True) [Brennan = yes 2026-10-18] - pipe leg: crossing to the pipe tip (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); Y@REF: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-04-04-FG col "Y FLATS" = "0.562" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 549.0, page verified True) [Brennan = yes 2026-10-18] - forged body hex across flats (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); D@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-04-04-FG col "B1 DRILL" = "0.172" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 549.0, page verified True) [Brennan = yes 2026-10-18] - JIC-leg bore (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); D1@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-04-04-FG col "A2 DRILL" = "0.281" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 549.0, page verified True) [Brennan = yes 2026-10-18] - pipe drill (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); THDMAJ_B@DRIVE: end library: male JIC -04 thread major = 0.4375 (gen_straight2 JIC[4] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A@DRIVE: end library: pipe OD of the -04 NPTF thread = 0.54 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[4], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes (format of the table's other 2501-LL rows); = OMi Items Side 1 / Side 2 Thread and Brennan TFA p.24 B1 SAE 37Deg / A2 NPTF</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-04-04 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-04-04 dims are NOT assumed; confirm before modelling | BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-04-04 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate)</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -1535,6 +1597,11 @@
       <c r="O20" t="inlineStr">
         <is>
           <t>2501-LL-04-04-FG</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1544,24 +1611,50 @@
           <t>2501-LL-06-04-FG</t>
         </is>
       </c>
+      <c r="B21" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="C21" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.5620000000000001</v>
+      </c>
+      <c r="E21" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0.54</v>
+      </c>
       <c r="I21" t="inlineStr">
         <is>
           <t>2501-LL-06-04-FG</t>
         </is>
       </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>9/16-18 (JIC) x 1/4-18 (NPTF) N4 long pattern</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-LL-06-04 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-LL-06-04 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): M@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-06-04-FG col "M LGTH" = "1.06" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 579.2, page verified True) [Brennan = yes 2026-10-18] - JIC leg: crossing to the JIC tip (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); N4@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-06-04-FG col "L LGTH" = "2.07" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 579.2, page verified True) [Brennan = yes 2026-10-18] - pipe leg: crossing to the pipe tip (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); Y@REF: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-06-04-FG col "Y FLATS" = "0.562" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 579.2, page verified True) [Brennan = yes 2026-10-18] - forged body hex across flats (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); D@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-06-04-FG col "B1 DRILL" = "0.297" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 579.2, page verified True) [Brennan = yes 2026-10-18] - JIC-leg bore (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); D1@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-06-04-FG col "A2 DRILL" = "0.281" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 579.2, page verified True) [Brennan = yes 2026-10-18] - pipe drill (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); THDMAJ_B@DRIVE: end library: male JIC -06 thread major = 0.5625 (gen_straight2 JIC[6] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A@DRIVE: end library: pipe OD of the -04 NPTF thread = 0.54 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[4], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes (format of the table's other 2501-LL rows); = OMi Items Side 1 / Side 2 Thread and Brennan TFA p.24 B1 SAE 37Deg / A2 NPTF</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-06-04 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-06-04 dims are NOT assumed; confirm before modelling | BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-06-04 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate)</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -1572,6 +1665,11 @@
       <c r="O21" t="inlineStr">
         <is>
           <t>2501-LL-06-04-FG</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1581,24 +1679,50 @@
           <t>2501-LL-06-06-FG</t>
         </is>
       </c>
+      <c r="B22" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="C22" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.5625</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.675</v>
+      </c>
       <c r="I22" t="inlineStr">
         <is>
           <t>2501-LL-06-06-FG</t>
         </is>
       </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>9/16-18 (JIC) x 3/8-18 (NPTF) N4 long pattern</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-LL-06-06 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-LL-06-06 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): M@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-06-06-FG col "M LGTH" = "1.14" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 589.3, page verified True) [Brennan = yes 2026-10-18] - JIC leg: crossing to the JIC tip (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); N4@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-06-06-FG col "L LGTH" = "2.42" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 589.3, page verified True) [Brennan = yes 2026-10-18] - pipe leg: crossing to the pipe tip (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); Y@REF: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-06-06-FG col "Y FLATS" = "0.750" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 589.3, page verified True) [Brennan = yes 2026-10-18] - forged body hex across flats (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); D@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-06-06-FG col "B1 DRILL" = "0.297" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 589.3, page verified True) [Brennan = yes 2026-10-18] - JIC-leg bore (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); D1@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-06-06-FG col "A2 DRILL" = "0.406" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 589.3, page verified True) [Brennan = yes 2026-10-18] - pipe drill (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); THDMAJ_B@DRIVE: end library: male JIC -06 thread major = 0.5625 (gen_straight2 JIC[6] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A@DRIVE: end library: pipe OD of the -06 NPTF thread = 0.675 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[6], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes (format of the table's other 2501-LL rows); = OMi Items Side 1 / Side 2 Thread and Brennan TFA p.24 B1 SAE 37Deg / A2 NPTF</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-06-06 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-06-06 dims are NOT assumed; confirm before modelling | BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-06-06 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate)</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -1609,6 +1733,11 @@
       <c r="O22" t="inlineStr">
         <is>
           <t>2501-LL-06-06-FG</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1655,24 +1784,50 @@
           <t>2501-LL-12-12-FG</t>
         </is>
       </c>
+      <c r="B24" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C24" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="D24" t="n">
+        <v>1.062</v>
+      </c>
+      <c r="E24" t="n">
+        <v>0.609</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.719</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.0625</v>
+      </c>
+      <c r="H24" t="n">
+        <v>1.05</v>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>2501-LL-12-12-FG</t>
         </is>
       </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>1 1/16-12 (JIC) x 3/4-14 (NPTF) N4 long pattern</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-LL-12-12 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-LL-12-12 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): M@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-12-12-FG col "M LGTH" = "1.660" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 659.8, page verified True) [Brennan = yes 2026-10-18] - JIC leg: crossing to the JIC tip (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); N4@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-12-12-FG col "L LGTH" = "3.280" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 659.8, page verified True) [Brennan = yes 2026-10-18] - pipe leg: crossing to the pipe tip (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); Y@REF: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-12-12-FG col "Y FLATS" = "1.062" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 659.8, page verified True) [Brennan = yes 2026-10-18] - forged body hex across flats (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); D@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-12-12-FG col "B1 DRILL" = "0.609" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 659.8, page verified True) [Brennan = yes 2026-10-18] - JIC-leg bore (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); D1@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-12-12-FG col "A2 DRILL" = "0.719" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 659.8, page verified True) [Brennan = yes 2026-10-18] - pipe drill (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); THDMAJ_B@DRIVE: end library: male JIC -12 thread major = 1.0625 (gen_straight2 JIC[12] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A@DRIVE: end library: pipe OD of the -12 NPTF thread = 1.05 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[12], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes (format of the table's other 2501-LL rows); = OMi Items Side 1 / Side 2 Thread and Brennan TFA p.24 B1 SAE 37Deg / A2 NPTF</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-12-12 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-12-12 dims are NOT assumed; confirm before modelling | BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-12-12 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate)</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -1683,6 +1838,11 @@
       <c r="O24" t="inlineStr">
         <is>
           <t>2501-LL-12-12-FG</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
@@ -1692,24 +1852,50 @@
           <t>2501-LL-16-16-FG</t>
         </is>
       </c>
+      <c r="B25" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="C25" t="n">
+        <v>4.05</v>
+      </c>
+      <c r="D25" t="n">
+        <v>1.312</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.9379999999999999</v>
+      </c>
+      <c r="G25" t="n">
+        <v>1.3125</v>
+      </c>
+      <c r="H25" t="n">
+        <v>1.315</v>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>2501-LL-16-16-FG</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>1 5/16-12 (JIC) x 1-11 1/2 (NPTF) N4 long pattern</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-LL-16-16 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-18] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-LL-16-16 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): M@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-16-16-FG col "M LGTH" = "1.81" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 690.1, page verified True) [Brennan = yes 2026-10-18] - JIC leg: crossing to the JIC tip (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); N4@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-16-16-FG col "L LGTH" = "4.05" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 690.1, page verified True) [Brennan = yes 2026-10-18] - pipe leg: crossing to the pipe tip (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); Y@REF: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-16-16-FG col "Y FLATS" = "1.312" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 690.1, page verified True) [Brennan = yes 2026-10-18] - forged body hex across flats (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); D@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-16-16-FG col "B1 DRILL" = "0.844" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 690.1, page verified True) [Brennan = yes 2026-10-18] - JIC-leg bore (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); D1@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-16-16-FG col "A2 DRILL" = "0.938" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 690.1, page verified True) [Brennan = yes 2026-10-18] - pipe drill (pairing as the FOLDS pilot 2501-LL-08-08-FG STEP, tools/measure/elbow90.py); THDMAJ_B@DRIVE: end library: male JIC -16 thread major = 1.3125 (gen_straight2 JIC[16] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A@DRIVE: end library: pipe OD of the -16 NPTF thread = 1.315 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[16], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Threads: thread callouts from the part number dashes (format of the table's other 2501-LL rows); = OMi Items Side 1 / Side 2 Thread and Brennan TFA p.24 B1 SAE 37Deg / A2 NPTF</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-16-16 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-16-16 dims are NOT assumed; confirm before modelling | BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-16-16 dims are NOT assumed; confirm before modelling | 2026-10-18 Brennan = yes (staged, not shipped): filled from Brennan only ($PRP@DimSource BRENNAN; to undo set the row MISSING and regenerate)</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -1720,6 +1906,11 @@
       <c r="O25" t="inlineStr">
         <is>
           <t>2501-LL-16-16-FG</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>

--- a/04_DESIGN_TABLES/DesignTable_2501LL.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_2501LL.xlsx
@@ -1747,24 +1747,50 @@
           <t>2501-LL-08-08-FG</t>
         </is>
       </c>
+      <c r="B23" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="C23" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.875</v>
+      </c>
+      <c r="E23" t="n">
+        <v>0.391</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.531</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="H23" t="n">
+        <v>0.84</v>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>2501-LL-08-08-FG</t>
         </is>
       </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>3/4-16 (JIC) x 1/2-14 (NPTF) N4 long pattern</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>MISSING</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-LL-08-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied</t>
+          <t>[BRENNAN-ONLY 2026-10-21] OMi catalog SKU (omindustrial.com collections feed (cs-adapters, carbon-steel-flange-adapters-accessories, carbon-steel-braze-beaded-hose; products.json limit=50, single pass 2026-09-23)); Air-Way has this size only as 2501-LL-08-08 (differs by -FG/-UNPL suffix) -&gt; dims NOT copied -&gt; 2026-10-21 (batch 19 C, staged): Brennan allowed (user 2026-10-18 "yes use brennan but still differentiate"); Air-Way prints no value for this part number, OMi's website file gives no dimension; sizes from the Brennan TFA catalog, each checked on the part's OWN Brennan STEP (09_STEP_FILES/BRENNAN_2501-LL-08-08-FG.stp, every value equal to the catalog within 0.005); end details from the end library: M@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-08-08-FG col "M LGTH" = "1.330" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 629.6, page verified True) [Brennan = yes 2026-10-18] - JIC leg: crossing to the JIC tip; own STEP: JIC tip 1.33, JIC end 0.657 = JIC[8] chain (C_ownstep/measure/2501-LL-08-08-FG.txt (elbow90.py / nptfm40.py --leg)); N4@DRIVE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-08-08-FG col "L LGTH" = "2.870" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 629.6, page verified True) [Brennan = yes 2026-10-18] - pipe leg: crossing to the NPTF tip; own STEP: pipe tip 2.87, male NPTF end 0.75 = ENDL[8], arm runs on to the end (C_ownstep/measure/2501-LL-08-08-FG.txt (elbow90.py / nptfm40.py --leg)); Y@REF: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-08-08-FG col "Y FLATS" = "0.875" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 629.6, page verified True) [Brennan = yes 2026-10-18] - forged body hex; own STEP: flats 0.875 on both arms (C_ownstep/measure/2501-LL-08-08-FG.txt (elbow90.py / nptfm40.py --leg)); D@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-08-08-FG col "B1 DRILL" = "0.391" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 629.6, page verified True) [Brennan = yes 2026-10-18] - JIC-leg bore; own STEP: JIC-leg bore 0.391 (C_ownstep/measure/2501-LL-08-08-FG.txt (elbow90.py / nptfm40.py --leg)); D1@BORE: Brennan TFA catalog p.24 table TFA-p024-t02 "2501-LL-FG MJ-MP 90 DEG ELBOW X-LONG" row 2501-LL-08-08-FG col "A2 DRILL" = "0.531" (07_RAW_EXTRACTS/brennan_catalogs/TFA Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 629.6, page verified True) [Brennan = yes 2026-10-18] - pipe drill; own STEP: pipe-leg bore 0.531 (C_ownstep/measure/2501-LL-08-08-FG.txt (elbow90.py / nptfm40.py --leg)); THDMAJ_B@DRIVE: end library: male JIC -08 thread major = 0.75 (gen_straight2 JIC[8] = MS33656J chain of templates/DesignTable_2403_SW2.xlsx, VERIFIED vs Brennan) [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_A@DRIVE: end library: pipe OD of the -08 NPTF thread = 0.84 (ASME B1.20.1 Table 2, tools generators/ms51500.py NPTF[8], as on every built pipe end; thread from the part number) [Q-TRANSFER-ENDLIB yes 2026-10-08]</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-08-08 dims are NOT assumed; confirm before modelling</t>
+          <t>BUILD-NEAR: forged (-FG) and non-FG variants differ in length on other series, so 2501-LL-08-08 dims are NOT assumed; confirm before modelling | 2026-10-21 batch 19 C (staged, not shipped): filled from the Brennan TFA catalog, checked on the own STEP (tools/_out/batch19_20261021/C_ownstep/measure); marked $PRP@DimSource BRENNAN (to undo: clear the BRENNAN cells, set the row MISSING, regenerate). Cross-check only: Air-Way 2501-LL-8-8 (plain): M 1.31 N4 2.88 Y 0.94 D 0.39 D1 0.53 (Y differs: forged flats 0.875)</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
@@ -1775,6 +1801,11 @@
       <c r="O23" t="inlineStr">
         <is>
           <t>2501-LL-08-08-FG</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>BRENNAN</t>
         </is>
       </c>
     </row>
